--- a/premise/data/additional_inventories/lci-batteries-NMC111-811-NCA-LFP.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC111-811-NCA-LFP.xlsx
@@ -1346,15 +1346,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N867"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46.5" customWidth="1"/>
     <col min="2" max="2" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>204</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ns3:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ns3:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ns3:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ns3:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ns3:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1410,12 +1410,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ns3:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>295</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ns3:dyDescent="0.2">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ns3:dyDescent="0.2">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ns3:dyDescent="0.2">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ns3:dyDescent="0.2">
       <c r="A15" t="s">
         <v>294</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ns3:dyDescent="0.2">
       <c r="A16" t="s">
         <v>61</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>290</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
@@ -1583,7 +1583,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ns3:dyDescent="0.2">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ns3:dyDescent="0.2">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ns3:dyDescent="0.2">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ns3:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ns3:dyDescent="0.2">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ns3:dyDescent="0.2">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1631,12 +1631,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ns3:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ns3:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ns3:dyDescent="0.2">
       <c r="A28" t="s">
         <v>290</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ns3:dyDescent="0.2">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ns3:dyDescent="0.2">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ns3:dyDescent="0.2">
       <c r="A31" t="s">
         <v>20</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ns3:dyDescent="0.2">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ns3:dyDescent="0.2">
       <c r="A33" t="s">
         <v>24</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ns3:dyDescent="0.2">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ns3:dyDescent="0.2">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ns3:dyDescent="0.2">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ns3:dyDescent="0.2">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ns3:dyDescent="0.2">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ns3:dyDescent="0.2">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ns3:dyDescent="0.2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ns3:dyDescent="0.2">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ns3:dyDescent="0.2">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ns3:dyDescent="0.2">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ns3:dyDescent="0.2">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ns3:dyDescent="0.2">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>0</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ns3:dyDescent="0.2">
       <c r="A48" t="s">
         <v>1</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ns3:dyDescent="0.2">
       <c r="A49" t="s">
         <v>3</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ns3:dyDescent="0.2">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ns3:dyDescent="0.2">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ns3:dyDescent="0.2">
       <c r="A52" t="s">
         <v>7</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ns3:dyDescent="0.2">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -2072,12 +2072,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ns3:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ns3:dyDescent="0.2">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ns3:dyDescent="0.2">
       <c r="A56" t="s">
         <v>20</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ns3:dyDescent="0.2">
       <c r="A57" t="s">
         <v>52</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ns3:dyDescent="0.2">
       <c r="A58" t="s">
         <v>55</v>
       </c>
@@ -2157,7 +2157,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ns3:dyDescent="0.2">
       <c r="A59" t="s">
         <v>57</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ns3:dyDescent="0.2">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ns3:dyDescent="0.2">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ns3:dyDescent="0.2">
       <c r="A62" t="s">
         <v>15</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ns3:dyDescent="0.2">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ns3:dyDescent="0.2">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6" ns3:dyDescent="0.2">
       <c r="A65" t="s">
         <v>33</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" ns3:dyDescent="0.2">
       <c r="A66" t="s">
         <v>41</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ns3:dyDescent="0.2">
       <c r="A67" t="s">
         <v>43</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6" ns3:dyDescent="0.2">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6" ns3:dyDescent="0.2">
       <c r="A69" t="s">
         <v>37</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:6" ns3:dyDescent="0.2">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:6" ns3:dyDescent="0.2">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>0</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:6" ns3:dyDescent="0.2">
       <c r="A74" t="s">
         <v>1</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:6" ns3:dyDescent="0.2">
       <c r="A75" t="s">
         <v>3</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ns3:dyDescent="0.2">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:6" ns3:dyDescent="0.2">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:6" ns3:dyDescent="0.2">
       <c r="A78" t="s">
         <v>7</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6" ns3:dyDescent="0.2">
       <c r="A79" t="s">
         <v>9</v>
       </c>
@@ -2473,12 +2473,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6" ns3:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ns3:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ns3:dyDescent="0.2">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ns3:dyDescent="0.2">
       <c r="A83" t="s">
         <v>65</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ns3:dyDescent="0.2">
       <c r="A84" t="s">
         <v>67</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ns3:dyDescent="0.2">
       <c r="A85" t="s">
         <v>69</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ns3:dyDescent="0.2">
       <c r="A86" t="s">
         <v>70</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ns3:dyDescent="0.2">
       <c r="A87" t="s">
         <v>72</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6" ns3:dyDescent="0.2">
       <c r="A88" t="s">
         <v>74</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ns3:dyDescent="0.2">
       <c r="A89" t="s">
         <v>75</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>0</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ns3:dyDescent="0.2">
       <c r="A92" t="s">
         <v>1</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ns3:dyDescent="0.2">
       <c r="A93" t="s">
         <v>3</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ns3:dyDescent="0.2">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ns3:dyDescent="0.2">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ns3:dyDescent="0.2">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ns3:dyDescent="0.2">
       <c r="A97" t="s">
         <v>9</v>
       </c>
@@ -2714,12 +2714,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ns3:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ns3:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ns3:dyDescent="0.2">
       <c r="A100" t="s">
         <v>69</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6" ns3:dyDescent="0.2">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ns3:dyDescent="0.2">
       <c r="A102" t="s">
         <v>77</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ns3:dyDescent="0.2">
       <c r="A103" t="s">
         <v>35</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ns3:dyDescent="0.2">
       <c r="A104" t="s">
         <v>79</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ns3:dyDescent="0.2">
       <c r="A105" t="s">
         <v>81</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ns3:dyDescent="0.2">
       <c r="A106" t="s">
         <v>67</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ns3:dyDescent="0.2">
       <c r="A107" t="s">
         <v>83</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:6" ns3:dyDescent="0.2">
       <c r="A108" t="s">
         <v>85</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ns3:dyDescent="0.2">
       <c r="A109" t="s">
         <v>87</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ns3:dyDescent="0.2">
       <c r="A110" t="s">
         <v>72</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ns3:dyDescent="0.2">
       <c r="A111" t="s">
         <v>70</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ns3:dyDescent="0.2">
       <c r="A112" t="s">
         <v>89</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ns3:dyDescent="0.2">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ns3:dyDescent="0.2">
       <c r="A114" t="s">
         <v>93</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ns3:dyDescent="0.2">
       <c r="A115" t="s">
         <v>95</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" ns3:dyDescent="0.2">
       <c r="A116" t="s">
         <v>95</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>0</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ns3:dyDescent="0.2">
       <c r="A119" t="s">
         <v>1</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ns3:dyDescent="0.2">
       <c r="A120" t="s">
         <v>3</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ns3:dyDescent="0.2">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ns3:dyDescent="0.2">
       <c r="A122" t="s">
         <v>6</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ns3:dyDescent="0.2">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ns3:dyDescent="0.2">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -3135,12 +3135,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ns3:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ns3:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ns3:dyDescent="0.2">
       <c r="A127" t="s">
         <v>74</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ns3:dyDescent="0.2">
       <c r="A128" t="s">
         <v>70</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:6" ns3:dyDescent="0.2">
       <c r="A129" t="s">
         <v>35</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:6" ns3:dyDescent="0.2">
       <c r="A130" t="s">
         <v>33</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:6" ns3:dyDescent="0.2">
       <c r="A131" t="s">
         <v>98</v>
       </c>
@@ -3260,7 +3260,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:6" ns3:dyDescent="0.2">
       <c r="A132" t="s">
         <v>98</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>0</v>
       </c>
@@ -3288,7 +3288,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6" ns3:dyDescent="0.2">
       <c r="A135" t="s">
         <v>1</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6" ns3:dyDescent="0.2">
       <c r="A136" t="s">
         <v>3</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:6" ns3:dyDescent="0.2">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6" ns3:dyDescent="0.2">
       <c r="A138" t="s">
         <v>6</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ns3:dyDescent="0.2">
       <c r="A139" t="s">
         <v>7</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6" ns3:dyDescent="0.2">
       <c r="A140" t="s">
         <v>9</v>
       </c>
@@ -3336,12 +3336,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6" ns3:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:6" ns3:dyDescent="0.2">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ns3:dyDescent="0.2">
       <c r="A143" t="s">
         <v>65</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6" ns3:dyDescent="0.2">
       <c r="A144" t="s">
         <v>101</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" ns3:dyDescent="0.2">
       <c r="A145" t="s">
         <v>72</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ns3:dyDescent="0.2">
       <c r="A146" t="s">
         <v>85</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ns3:dyDescent="0.2">
       <c r="A147" t="s">
         <v>103</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ns3:dyDescent="0.2">
       <c r="A148" t="s">
         <v>105</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ns3:dyDescent="0.2">
       <c r="A149" t="s">
         <v>35</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ns3:dyDescent="0.2">
       <c r="A150" t="s">
         <v>70</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ns3:dyDescent="0.2">
       <c r="A151" t="s">
         <v>107</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ns3:dyDescent="0.2">
       <c r="A152" t="s">
         <v>67</v>
       </c>
@@ -3561,7 +3561,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ns3:dyDescent="0.2">
       <c r="A153" t="s">
         <v>75</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ns3:dyDescent="0.2">
       <c r="A154" t="s">
         <v>109</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6" ns3:dyDescent="0.2">
       <c r="A155" t="s">
         <v>109</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ns3:dyDescent="0.2">
       <c r="A156" t="s">
         <v>98</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ns3:dyDescent="0.2">
       <c r="A157" t="s">
         <v>98</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A159" s="2" t="s">
         <v>0</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6" ns3:dyDescent="0.2">
       <c r="A160" t="s">
         <v>1</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" ns3:dyDescent="0.2">
       <c r="A161" t="s">
         <v>3</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" ns3:dyDescent="0.2">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A163" t="s">
         <v>6</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" ns3:dyDescent="0.2">
       <c r="A164" t="s">
         <v>7</v>
       </c>
@@ -3709,12 +3709,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A165" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:6" ns3:dyDescent="0.2">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A167" s="9" t="s">
         <v>296</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:6" ns3:dyDescent="0.2">
       <c r="A168" t="s">
         <v>57</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" ns3:dyDescent="0.2">
       <c r="A169" t="s">
         <v>52</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" ns3:dyDescent="0.2">
       <c r="A170" t="s">
         <v>59</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" ns3:dyDescent="0.2">
       <c r="A171" t="s">
         <v>294</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" ns3:dyDescent="0.2">
       <c r="A172" t="s">
         <v>61</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A173" s="9" t="s">
         <v>281</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A175" s="2" t="s">
         <v>0</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" ns3:dyDescent="0.2">
       <c r="A176" t="s">
         <v>1</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:6" ns3:dyDescent="0.2">
       <c r="A177" t="s">
         <v>3</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:6" ns3:dyDescent="0.2">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A179" t="s">
         <v>6</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:6" ns3:dyDescent="0.2">
       <c r="A180" t="s">
         <v>7</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:6" ns3:dyDescent="0.2">
       <c r="A181" t="s">
         <v>9</v>
       </c>
@@ -3930,12 +3930,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:6" ns3:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:6" ns3:dyDescent="0.2">
       <c r="A183" t="s">
         <v>11</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A184" t="s">
         <v>281</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:6" ns3:dyDescent="0.2">
       <c r="A185" t="s">
         <v>112</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:6" ns3:dyDescent="0.2">
       <c r="A186" t="s">
         <v>45</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:6" ns3:dyDescent="0.2">
       <c r="A187" t="s">
         <v>282</v>
       </c>
@@ -4035,7 +4035,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:6" ns3:dyDescent="0.2">
       <c r="A188" t="s">
         <v>115</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:6" ns3:dyDescent="0.2">
       <c r="A189" t="s">
         <v>116</v>
       </c>
@@ -4075,7 +4075,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:6" ns3:dyDescent="0.2">
       <c r="A190" t="s">
         <v>117</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:6" ns3:dyDescent="0.2">
       <c r="A191" t="s">
         <v>43</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:6" ns3:dyDescent="0.2">
       <c r="A192" t="s">
         <v>41</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:6" ns3:dyDescent="0.2">
       <c r="A193" t="s">
         <v>118</v>
       </c>
@@ -4155,7 +4155,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:6" ns3:dyDescent="0.2">
       <c r="A194" t="s">
         <v>15</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:6" ns3:dyDescent="0.2">
       <c r="A195" t="s">
         <v>39</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:6" ns3:dyDescent="0.2">
       <c r="A196" t="s">
         <v>119</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:6" ns3:dyDescent="0.2">
       <c r="A197" t="s">
         <v>63</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:6" ns3:dyDescent="0.2">
       <c r="A198" t="s">
         <v>85</v>
       </c>
@@ -4255,7 +4255,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:6" ns3:dyDescent="0.2">
       <c r="A199" t="s">
         <v>120</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:6" ns3:dyDescent="0.2">
       <c r="A200" t="s">
         <v>122</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>0</v>
       </c>
@@ -4303,7 +4303,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:6" ns3:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:6" ns3:dyDescent="0.2">
       <c r="A204" t="s">
         <v>3</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:6" ns3:dyDescent="0.2">
       <c r="A205" t="s">
         <v>5</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:6" ns3:dyDescent="0.2">
       <c r="A206" t="s">
         <v>6</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:6" ns3:dyDescent="0.2">
       <c r="A207" t="s">
         <v>7</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:6" ns3:dyDescent="0.2">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -4351,12 +4351,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" ns3:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" ns3:dyDescent="0.2">
       <c r="A210" t="s">
         <v>11</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" ns3:dyDescent="0.2">
       <c r="A211" t="s">
         <v>282</v>
       </c>
@@ -4396,7 +4396,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" ns3:dyDescent="0.2">
       <c r="A212" t="s">
         <v>124</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" ns3:dyDescent="0.2">
       <c r="A213" t="s">
         <v>55</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" ns3:dyDescent="0.2">
       <c r="A214" t="s">
         <v>61</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" ns3:dyDescent="0.2">
       <c r="A215" t="s">
         <v>45</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" ns3:dyDescent="0.2">
       <c r="A216" t="s">
         <v>125</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" ns3:dyDescent="0.2">
       <c r="A217" t="s">
         <v>127</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" ns3:dyDescent="0.2">
       <c r="A218" t="s">
         <v>112</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" ns3:dyDescent="0.2">
       <c r="A219" t="s">
         <v>129</v>
       </c>
@@ -4556,7 +4556,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" ns3:dyDescent="0.2">
       <c r="A220" t="s">
         <v>122</v>
       </c>
@@ -4577,7 +4577,7 @@
       </c>
       <c r="G220" s="4"/>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" ns3:dyDescent="0.2">
       <c r="A221" t="s">
         <v>283</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A223" s="2" t="s">
         <v>0</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" ns3:dyDescent="0.2">
       <c r="A224" t="s">
         <v>1</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" ns3:dyDescent="0.2">
       <c r="A225" t="s">
         <v>3</v>
       </c>
@@ -4621,7 +4621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" ns3:dyDescent="0.2">
       <c r="A226" t="s">
         <v>5</v>
       </c>
@@ -4629,7 +4629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" ns3:dyDescent="0.2">
       <c r="A227" t="s">
         <v>6</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" ns3:dyDescent="0.2">
       <c r="A228" t="s">
         <v>7</v>
       </c>
@@ -4645,7 +4645,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" ns3:dyDescent="0.2">
       <c r="A229" t="s">
         <v>9</v>
       </c>
@@ -4653,12 +4653,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" ns3:dyDescent="0.2">
       <c r="A230" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" ns3:dyDescent="0.2">
       <c r="A231" t="s">
         <v>11</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" ns3:dyDescent="0.2">
       <c r="A232" t="s">
         <v>283</v>
       </c>
@@ -4701,7 +4701,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" ns3:dyDescent="0.2">
       <c r="A233" t="s">
         <v>124</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" ns3:dyDescent="0.2">
       <c r="A234" t="s">
         <v>132</v>
       </c>
@@ -4741,7 +4741,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" ns3:dyDescent="0.2">
       <c r="A235" t="s">
         <v>61</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" ns3:dyDescent="0.2">
       <c r="A236" t="s">
         <v>55</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" ns3:dyDescent="0.2">
       <c r="A237" t="s">
         <v>45</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" ns3:dyDescent="0.2">
       <c r="A238" t="s">
         <v>274</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" ns3:dyDescent="0.2">
       <c r="A239" t="s">
         <v>284</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" ns3:dyDescent="0.2">
       <c r="A240" t="s">
         <v>122</v>
       </c>
@@ -4861,7 +4861,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" ns3:dyDescent="0.2">
       <c r="A241" t="s">
         <v>134</v>
       </c>
@@ -4878,7 +4878,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" ns3:dyDescent="0.2">
       <c r="A242" t="s">
         <v>137</v>
       </c>
@@ -4895,10 +4895,10 @@
         <v>136</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" ns3:dyDescent="0.2">
       <c r="G243" s="4"/>
     </row>
-    <row r="244" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A244" s="2" t="s">
         <v>0</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" ns3:dyDescent="0.2">
       <c r="A245" t="s">
         <v>1</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" ns3:dyDescent="0.2">
       <c r="A246" t="s">
         <v>3</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" ns3:dyDescent="0.2">
       <c r="A247" t="s">
         <v>5</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" ns3:dyDescent="0.2">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -4938,7 +4938,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" ns3:dyDescent="0.2">
       <c r="A249" t="s">
         <v>7</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" ns3:dyDescent="0.2">
       <c r="A250" t="s">
         <v>9</v>
       </c>
@@ -4954,12 +4954,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" ns3:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" ns3:dyDescent="0.2">
       <c r="A252" t="s">
         <v>11</v>
       </c>
@@ -4982,7 +4982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" ns3:dyDescent="0.2">
       <c r="A253" t="s">
         <v>284</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" ns3:dyDescent="0.2">
       <c r="A254" t="s">
         <v>132</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" ns3:dyDescent="0.2">
       <c r="A255" t="s">
         <v>55</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" ns3:dyDescent="0.2">
       <c r="A256" t="s">
         <v>124</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" ns3:dyDescent="0.2">
       <c r="A257" t="s">
         <v>61</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" ns3:dyDescent="0.2">
       <c r="A258" t="s">
         <v>112</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" ns3:dyDescent="0.2">
       <c r="A259" t="s">
         <v>141</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" ns3:dyDescent="0.2">
       <c r="A260" t="s">
         <v>273</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" ns3:dyDescent="0.2">
       <c r="A261" t="s">
         <v>144</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" ns3:dyDescent="0.2">
       <c r="A262" t="s">
         <v>146</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" ns3:dyDescent="0.2">
       <c r="A263" t="s">
         <v>148</v>
       </c>
@@ -5202,7 +5202,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" ns3:dyDescent="0.2">
       <c r="A264" t="s">
         <v>122</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" ns3:dyDescent="0.2">
       <c r="A265" t="s">
         <v>150</v>
       </c>
@@ -5242,7 +5242,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" ns3:dyDescent="0.2">
       <c r="A266" t="s">
         <v>152</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" ns3:dyDescent="0.2">
       <c r="A267" t="s">
         <v>153</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>0</v>
       </c>
@@ -5284,7 +5284,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" ns3:dyDescent="0.2">
       <c r="A270" t="s">
         <v>1</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" ns3:dyDescent="0.2">
       <c r="A271" t="s">
         <v>3</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" ns3:dyDescent="0.2">
       <c r="A272" t="s">
         <v>5</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" ns3:dyDescent="0.2">
       <c r="A273" t="s">
         <v>6</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" ns3:dyDescent="0.2">
       <c r="A274" t="s">
         <v>7</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" ns3:dyDescent="0.2">
       <c r="A275" t="s">
         <v>9</v>
       </c>
@@ -5332,12 +5332,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" ns3:dyDescent="0.2">
       <c r="A276" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" ns3:dyDescent="0.2">
       <c r="A277" t="s">
         <v>11</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" ns3:dyDescent="0.2">
       <c r="A278" t="s">
         <v>115</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" ns3:dyDescent="0.2">
       <c r="A279" t="s">
         <v>124</v>
       </c>
@@ -5400,7 +5400,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" ns3:dyDescent="0.2">
       <c r="A280" t="s">
         <v>61</v>
       </c>
@@ -5420,7 +5420,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" ns3:dyDescent="0.2">
       <c r="A281" t="s">
         <v>55</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" ns3:dyDescent="0.2">
       <c r="A282" t="s">
         <v>305</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" ns3:dyDescent="0.2">
       <c r="A283" t="s">
         <v>307</v>
       </c>
@@ -5480,7 +5480,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" ns3:dyDescent="0.2">
       <c r="A284" t="s">
         <v>155</v>
       </c>
@@ -5500,7 +5500,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" ns3:dyDescent="0.2">
       <c r="A285" t="s">
         <v>45</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" ns3:dyDescent="0.2">
       <c r="A286" t="s">
         <v>157</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" ns3:dyDescent="0.2">
       <c r="A287" t="s">
         <v>125</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" ns3:dyDescent="0.2">
       <c r="A288" t="s">
         <v>150</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11" ns3:dyDescent="0.2">
       <c r="A289" t="s">
         <v>122</v>
       </c>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="K289" s="4"/>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11" ns3:dyDescent="0.2">
       <c r="A290" t="s">
         <v>112</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11" ns3:dyDescent="0.2">
       <c r="A291" t="s">
         <v>159</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A293" s="2" t="s">
         <v>0</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11" ns3:dyDescent="0.2">
       <c r="A294" t="s">
         <v>1</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11" ns3:dyDescent="0.2">
       <c r="A295" t="s">
         <v>3</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11" ns3:dyDescent="0.2">
       <c r="A296" t="s">
         <v>5</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11" ns3:dyDescent="0.2">
       <c r="A297" t="s">
         <v>6</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11" ns3:dyDescent="0.2">
       <c r="A298" t="s">
         <v>7</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11" ns3:dyDescent="0.2">
       <c r="A299" t="s">
         <v>9</v>
       </c>
@@ -5697,12 +5697,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11" ns3:dyDescent="0.2">
       <c r="A300" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11" ns3:dyDescent="0.2">
       <c r="A301" t="s">
         <v>11</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11" ns3:dyDescent="0.2">
       <c r="A302" t="s">
         <v>116</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11" ns3:dyDescent="0.2">
       <c r="A303" t="s">
         <v>122</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11" ns3:dyDescent="0.2">
       <c r="A304" t="s">
         <v>161</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" ns3:dyDescent="0.2">
       <c r="A305" t="s">
         <v>163</v>
       </c>
@@ -5805,7 +5805,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" ns3:dyDescent="0.2">
       <c r="A306" t="s">
         <v>164</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" ns3:dyDescent="0.2">
       <c r="A307" t="s">
         <v>45</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" ns3:dyDescent="0.2">
       <c r="A308" t="s">
         <v>166</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A310" s="2" t="s">
         <v>0</v>
       </c>
@@ -5873,7 +5873,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" ns3:dyDescent="0.2">
       <c r="A311" t="s">
         <v>1</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" ns3:dyDescent="0.2">
       <c r="A312" t="s">
         <v>3</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" ns3:dyDescent="0.2">
       <c r="A313" t="s">
         <v>5</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" ns3:dyDescent="0.2">
       <c r="A314" t="s">
         <v>6</v>
       </c>
@@ -5905,7 +5905,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" ns3:dyDescent="0.2">
       <c r="A315" t="s">
         <v>7</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" ns3:dyDescent="0.2">
       <c r="A316" t="s">
         <v>9</v>
       </c>
@@ -5921,12 +5921,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" ns3:dyDescent="0.2">
       <c r="A317" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" ns3:dyDescent="0.2">
       <c r="A318" t="s">
         <v>11</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" ns3:dyDescent="0.2">
       <c r="A319" t="s">
         <v>117</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" ns3:dyDescent="0.2">
       <c r="A320" t="s">
         <v>59</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" ns3:dyDescent="0.2">
       <c r="A321" t="s">
         <v>61</v>
       </c>
@@ -6009,7 +6009,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" ns3:dyDescent="0.2">
       <c r="A322" t="s">
         <v>52</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" ns3:dyDescent="0.2">
       <c r="A323" t="s">
         <v>57</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" ns3:dyDescent="0.2">
       <c r="A324" t="s">
         <v>55</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" ns3:dyDescent="0.2">
       <c r="A325" t="s">
         <v>43</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" ns3:dyDescent="0.2">
       <c r="A326" t="s">
         <v>50</v>
       </c>
@@ -6109,7 +6109,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" ns3:dyDescent="0.2">
       <c r="A327" t="s">
         <v>89</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" ns3:dyDescent="0.2">
       <c r="A328" t="s">
         <v>141</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" ns3:dyDescent="0.2">
       <c r="A329" t="s">
         <v>168</v>
       </c>
@@ -6169,7 +6169,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" ns3:dyDescent="0.2">
       <c r="A330" t="s">
         <v>168</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" ns3:dyDescent="0.2">
       <c r="A331" t="s">
         <v>168</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" ns3:dyDescent="0.2">
       <c r="A332" t="s">
         <v>171</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" ns3:dyDescent="0.2">
       <c r="A333" t="s">
         <v>171</v>
       </c>
@@ -6249,7 +6249,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A335" s="2" t="s">
         <v>0</v>
       </c>
@@ -6257,7 +6257,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" ns3:dyDescent="0.2">
       <c r="A336" t="s">
         <v>1</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" ns3:dyDescent="0.2">
       <c r="A337" t="s">
         <v>3</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" ns3:dyDescent="0.2">
       <c r="A338" t="s">
         <v>5</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" ns3:dyDescent="0.2">
       <c r="A339" t="s">
         <v>6</v>
       </c>
@@ -6289,7 +6289,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" ns3:dyDescent="0.2">
       <c r="A340" t="s">
         <v>7</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" ns3:dyDescent="0.2">
       <c r="A341" t="s">
         <v>9</v>
       </c>
@@ -6305,12 +6305,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" ns3:dyDescent="0.2">
       <c r="A342" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" ns3:dyDescent="0.2">
       <c r="A343" t="s">
         <v>11</v>
       </c>
@@ -6333,7 +6333,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" ns3:dyDescent="0.2">
       <c r="A344" t="s">
         <v>118</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" ns3:dyDescent="0.2">
       <c r="A345" t="s">
         <v>55</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" ns3:dyDescent="0.2">
       <c r="A346" t="s">
         <v>61</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" ns3:dyDescent="0.2">
       <c r="A347" t="s">
         <v>52</v>
       </c>
@@ -6413,7 +6413,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" ns3:dyDescent="0.2">
       <c r="A348" t="s">
         <v>57</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" ns3:dyDescent="0.2">
       <c r="A349" t="s">
         <v>59</v>
       </c>
@@ -6453,7 +6453,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:7" ns3:dyDescent="0.2">
       <c r="A350" t="s">
         <v>141</v>
       </c>
@@ -6473,7 +6473,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:7" ns3:dyDescent="0.2">
       <c r="A351" t="s">
         <v>15</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:7" ns3:dyDescent="0.2">
       <c r="A352" t="s">
         <v>39</v>
       </c>
@@ -6513,7 +6513,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:7" ns3:dyDescent="0.2">
       <c r="A353" t="s">
         <v>173</v>
       </c>
@@ -6533,7 +6533,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:7" ns3:dyDescent="0.2">
       <c r="A354" t="s">
         <v>168</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:7" ns3:dyDescent="0.2">
       <c r="A355" t="s">
         <v>168</v>
       </c>
@@ -6573,7 +6573,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:7" ns3:dyDescent="0.2">
       <c r="A356" t="s">
         <v>168</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:7" ns3:dyDescent="0.2">
       <c r="A357" t="s">
         <v>171</v>
       </c>
@@ -6613,7 +6613,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:7" ns3:dyDescent="0.2">
       <c r="A358" t="s">
         <v>171</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A360" s="2" t="s">
         <v>0</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:7" ns3:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1</v>
       </c>
@@ -6649,7 +6649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:7" ns3:dyDescent="0.2">
       <c r="A362" t="s">
         <v>3</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:7" ns3:dyDescent="0.2">
       <c r="A363" t="s">
         <v>5</v>
       </c>
@@ -6665,7 +6665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:7" ns3:dyDescent="0.2">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -6673,7 +6673,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:7" ns3:dyDescent="0.2">
       <c r="A365" t="s">
         <v>7</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:7" ns3:dyDescent="0.2">
       <c r="A366" t="s">
         <v>9</v>
       </c>
@@ -6689,12 +6689,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:7" ns3:dyDescent="0.2">
       <c r="A367" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:7" ns3:dyDescent="0.2">
       <c r="A368" t="s">
         <v>11</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:7" ns3:dyDescent="0.2">
       <c r="A369" t="s">
         <v>119</v>
       </c>
@@ -6737,7 +6737,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:7" ns3:dyDescent="0.2">
       <c r="A370" t="s">
         <v>59</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:7" ns3:dyDescent="0.2">
       <c r="A371" t="s">
         <v>55</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:7" ns3:dyDescent="0.2">
       <c r="A372" t="s">
         <v>63</v>
       </c>
@@ -6797,7 +6797,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:7" ns3:dyDescent="0.2">
       <c r="A373" t="s">
         <v>37</v>
       </c>
@@ -6817,7 +6817,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:7" ns3:dyDescent="0.2">
       <c r="A374" t="s">
         <v>175</v>
       </c>
@@ -6837,7 +6837,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:7" ns3:dyDescent="0.2">
       <c r="A375" t="s">
         <v>177</v>
       </c>
@@ -6857,7 +6857,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:7" ns3:dyDescent="0.2">
       <c r="A376" t="s">
         <v>112</v>
       </c>
@@ -6877,7 +6877,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:7" ns3:dyDescent="0.2">
       <c r="A377" t="s">
         <v>127</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:7" ns3:dyDescent="0.2">
       <c r="A378" t="s">
         <v>179</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:7" ns3:dyDescent="0.2">
       <c r="A379" t="s">
         <v>181</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:7" ns3:dyDescent="0.2">
       <c r="A380" t="s">
         <v>45</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:7" ns3:dyDescent="0.2">
       <c r="A381" t="s">
         <v>122</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:7" ns3:dyDescent="0.2">
       <c r="A382" t="s">
         <v>183</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A384" s="2" t="s">
         <v>0</v>
       </c>
@@ -7005,7 +7005,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:6" ns3:dyDescent="0.2">
       <c r="A385" t="s">
         <v>1</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:6" ns3:dyDescent="0.2">
       <c r="A386" t="s">
         <v>3</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:6" ns3:dyDescent="0.2">
       <c r="A387" t="s">
         <v>5</v>
       </c>
@@ -7029,7 +7029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A388" t="s">
         <v>6</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:6" ns3:dyDescent="0.2">
       <c r="A389" t="s">
         <v>7</v>
       </c>
@@ -7045,12 +7045,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="390" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A390" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:6" ns3:dyDescent="0.2">
       <c r="A391" t="s">
         <v>11</v>
       </c>
@@ -7070,7 +7070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="392" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A392" s="9" t="s">
         <v>298</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:6" ns3:dyDescent="0.2">
       <c r="A393" t="s">
         <v>57</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:6" ns3:dyDescent="0.2">
       <c r="A394" t="s">
         <v>52</v>
       </c>
@@ -7130,7 +7130,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:6" ns3:dyDescent="0.2">
       <c r="A395" t="s">
         <v>59</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:6" ns3:dyDescent="0.2">
       <c r="A396" t="s">
         <v>294</v>
       </c>
@@ -7170,7 +7170,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:6" ns3:dyDescent="0.2">
       <c r="A397" t="s">
         <v>61</v>
       </c>
@@ -7190,7 +7190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="398" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A398" s="9" t="s">
         <v>285</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="400" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A400" s="2" t="s">
         <v>0</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:6" ns3:dyDescent="0.2">
       <c r="A401" t="s">
         <v>1</v>
       </c>
@@ -7226,7 +7226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:6" ns3:dyDescent="0.2">
       <c r="A402" t="s">
         <v>3</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:6" ns3:dyDescent="0.2">
       <c r="A403" t="s">
         <v>5</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A404" t="s">
         <v>6</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:6" ns3:dyDescent="0.2">
       <c r="A405" t="s">
         <v>7</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:6" ns3:dyDescent="0.2">
       <c r="A406" t="s">
         <v>9</v>
       </c>
@@ -7266,12 +7266,12 @@
         <v>286</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:6" ns3:dyDescent="0.2">
       <c r="A407" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:6" ns3:dyDescent="0.2">
       <c r="A408" t="s">
         <v>11</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A409" t="s">
         <v>285</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:6" ns3:dyDescent="0.2">
       <c r="A410" t="s">
         <v>112</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:6" ns3:dyDescent="0.2">
       <c r="A411" t="s">
         <v>45</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:6" ns3:dyDescent="0.2">
       <c r="A412" t="s">
         <v>287</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:6" ns3:dyDescent="0.2">
       <c r="A413" t="s">
         <v>115</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:6" ns3:dyDescent="0.2">
       <c r="A414" t="s">
         <v>116</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:6" ns3:dyDescent="0.2">
       <c r="A415" t="s">
         <v>117</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:6" ns3:dyDescent="0.2">
       <c r="A416" t="s">
         <v>43</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:6" ns3:dyDescent="0.2">
       <c r="A417" t="s">
         <v>41</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:6" ns3:dyDescent="0.2">
       <c r="A418" t="s">
         <v>118</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:6" ns3:dyDescent="0.2">
       <c r="A419" t="s">
         <v>15</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:6" ns3:dyDescent="0.2">
       <c r="A420" t="s">
         <v>39</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:6" ns3:dyDescent="0.2">
       <c r="A421" t="s">
         <v>119</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:6" ns3:dyDescent="0.2">
       <c r="A422" t="s">
         <v>63</v>
       </c>
@@ -7571,7 +7571,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:6" ns3:dyDescent="0.2">
       <c r="A423" t="s">
         <v>85</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:6" ns3:dyDescent="0.2">
       <c r="A424" t="s">
         <v>120</v>
       </c>
@@ -7611,7 +7611,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:6" ns3:dyDescent="0.2">
       <c r="A425" t="s">
         <v>122</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="427" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A427" s="2" t="s">
         <v>0</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:6" ns3:dyDescent="0.2">
       <c r="A428" t="s">
         <v>1</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:6" ns3:dyDescent="0.2">
       <c r="A429" t="s">
         <v>3</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:6" ns3:dyDescent="0.2">
       <c r="A430" t="s">
         <v>5</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:6" ns3:dyDescent="0.2">
       <c r="A431" t="s">
         <v>6</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:6" ns3:dyDescent="0.2">
       <c r="A432" t="s">
         <v>7</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:7" ns3:dyDescent="0.2">
       <c r="A433" t="s">
         <v>9</v>
       </c>
@@ -7687,12 +7687,12 @@
         <v>286</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:7" ns3:dyDescent="0.2">
       <c r="A434" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:7" ns3:dyDescent="0.2">
       <c r="A435" t="s">
         <v>11</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:7" ns3:dyDescent="0.2">
       <c r="A436" t="s">
         <v>287</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:7" ns3:dyDescent="0.2">
       <c r="A437" t="s">
         <v>124</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:7" ns3:dyDescent="0.2">
       <c r="A438" t="s">
         <v>55</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:7" ns3:dyDescent="0.2">
       <c r="A439" t="s">
         <v>61</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:7" ns3:dyDescent="0.2">
       <c r="A440" t="s">
         <v>45</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:7" ns3:dyDescent="0.2">
       <c r="A441" t="s">
         <v>125</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:7" ns3:dyDescent="0.2">
       <c r="A442" t="s">
         <v>127</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:7" ns3:dyDescent="0.2">
       <c r="A443" t="s">
         <v>112</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:7" ns3:dyDescent="0.2">
       <c r="A444" t="s">
         <v>129</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:7" ns3:dyDescent="0.2">
       <c r="A445" t="s">
         <v>122</v>
       </c>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="G445" s="4"/>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:7" ns3:dyDescent="0.2">
       <c r="A446" t="s">
         <v>288</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A448" s="2" t="s">
         <v>0</v>
       </c>
@@ -7941,15 +7941,17 @@
         <v>288</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:7" ns3:dyDescent="0.2">
       <c r="A449" t="s">
         <v>1</v>
       </c>
-      <c r="B449" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity). Preserve the original rounded anhydrous LiOH dose, precursor, output and energy boundary. Correct battery-grade monohydrate mass and add its water of crystallisation to the existing air emission. Existing reaction-water baseline is not validated by this change. NCA source includes 0.04 kg oxygen and 0.00024 m3 water; this workbook omits that oxygen and repeats the NMC811 water value. Those inherited reaction discrepancies need a separate correction. No complete reaction or whole-cell validation is claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" spans="1:7" ns3:dyDescent="0.2">
       <c r="A450" t="s">
         <v>3</v>
       </c>
@@ -7957,7 +7959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:7" ns3:dyDescent="0.2">
       <c r="A451" t="s">
         <v>5</v>
       </c>
@@ -7965,7 +7967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:7" ns3:dyDescent="0.2">
       <c r="A452" t="s">
         <v>6</v>
       </c>
@@ -7973,7 +7975,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:7" ns3:dyDescent="0.2">
       <c r="A453" t="s">
         <v>7</v>
       </c>
@@ -7981,7 +7983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:7" ns3:dyDescent="0.2">
       <c r="A454" t="s">
         <v>9</v>
       </c>
@@ -7989,12 +7991,12 @@
         <v>286</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:7" ns3:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:7" ns3:dyDescent="0.2">
       <c r="A456" t="s">
         <v>11</v>
       </c>
@@ -8016,8 +8018,13 @@
       <c r="G456" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" spans="1:7" ns3:dyDescent="0.2">
       <c r="A457" t="s">
         <v>288</v>
       </c>
@@ -8037,7 +8044,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:7" ns3:dyDescent="0.2">
       <c r="A458" t="s">
         <v>124</v>
       </c>
@@ -8057,7 +8064,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:7" ns3:dyDescent="0.2">
       <c r="A459" t="s">
         <v>132</v>
       </c>
@@ -8077,7 +8084,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:7" ns3:dyDescent="0.2">
       <c r="A460" t="s">
         <v>61</v>
       </c>
@@ -8097,7 +8104,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:7" ns3:dyDescent="0.2">
       <c r="A461" t="s">
         <v>55</v>
       </c>
@@ -8117,7 +8124,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:7" ns3:dyDescent="0.2">
       <c r="A462" t="s">
         <v>45</v>
       </c>
@@ -8137,12 +8144,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:7" ns3:dyDescent="0.2">
       <c r="A463" t="s">
         <v>276</v>
       </c>
       <c r="B463" s="3">
-        <v>0.246</v>
+        <v>0.4310624295318829</v>
       </c>
       <c r="C463" t="s">
         <v>8</v>
@@ -8156,8 +8163,13 @@
       <c r="G463" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1: preserve 0.246 kg anhydrous LiOH equivalent per kg oxide; purchase 0.4310624295318829 kg LiOH.H2O = 0.246 * 41.962 / 23.947. Atomic masses Li=6.94, H=1.008, O=15.999 g/mol. No additional yield or excess-lithium factor. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" spans="1:7" ns3:dyDescent="0.2">
       <c r="A464" t="s">
         <v>289</v>
       </c>
@@ -8177,7 +8189,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:7" ns3:dyDescent="0.2">
       <c r="A465" t="s">
         <v>122</v>
       </c>
@@ -8197,12 +8209,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:7" ns3:dyDescent="0.2">
       <c r="A466" t="s">
         <v>137</v>
       </c>
       <c r="B466" s="3">
-        <v>1.9562E-4</v>
+        <v>0.0003806824295318829</v>
       </c>
       <c r="C466" t="s">
         <v>138</v>
@@ -8213,11 +8225,16 @@
       <c r="F466" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1: retained inherited 0.00019562 m3 reaction-water baseline plus 0.1850624295318829 kg water of crystallisation / 1000 kg/m3. Assume bound water exits to air during calcination through the existing Water flow. This closes the hydration increment only; original reaction-water/oxygen balance remains unresolved. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" spans="1:7" ns3:dyDescent="0.2">
       <c r="G467" s="4"/>
     </row>
-    <row r="468" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A468" s="2" t="s">
         <v>0</v>
       </c>
@@ -8225,7 +8242,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:7" ns3:dyDescent="0.2">
       <c r="A469" t="s">
         <v>1</v>
       </c>
@@ -8233,7 +8250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:7" ns3:dyDescent="0.2">
       <c r="A470" t="s">
         <v>3</v>
       </c>
@@ -8241,7 +8258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:7" ns3:dyDescent="0.2">
       <c r="A471" t="s">
         <v>5</v>
       </c>
@@ -8249,7 +8266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:7" ns3:dyDescent="0.2">
       <c r="A472" t="s">
         <v>6</v>
       </c>
@@ -8257,7 +8274,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:7" ns3:dyDescent="0.2">
       <c r="A473" t="s">
         <v>7</v>
       </c>
@@ -8265,7 +8282,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:7" ns3:dyDescent="0.2">
       <c r="A474" t="s">
         <v>9</v>
       </c>
@@ -8273,12 +8290,12 @@
         <v>286</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:7" ns3:dyDescent="0.2">
       <c r="A475" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:7" ns3:dyDescent="0.2">
       <c r="A476" t="s">
         <v>11</v>
       </c>
@@ -8301,7 +8318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:7" ns3:dyDescent="0.2">
       <c r="A477" t="s">
         <v>289</v>
       </c>
@@ -8321,7 +8338,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:7" ns3:dyDescent="0.2">
       <c r="A478" t="s">
         <v>132</v>
       </c>
@@ -8341,7 +8358,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:7" ns3:dyDescent="0.2">
       <c r="A479" t="s">
         <v>55</v>
       </c>
@@ -8361,7 +8378,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:7" ns3:dyDescent="0.2">
       <c r="A480" t="s">
         <v>124</v>
       </c>
@@ -8381,7 +8398,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:14" ns3:dyDescent="0.2">
       <c r="A481" t="s">
         <v>61</v>
       </c>
@@ -8401,7 +8418,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:14" ns3:dyDescent="0.2">
       <c r="A482" t="s">
         <v>112</v>
       </c>
@@ -8421,7 +8438,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:14" ns3:dyDescent="0.2">
       <c r="A483" t="s">
         <v>141</v>
       </c>
@@ -8441,7 +8458,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:14" ns3:dyDescent="0.2">
       <c r="A484" t="s">
         <v>273</v>
       </c>
@@ -8461,7 +8478,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:14" ns3:dyDescent="0.2">
       <c r="A485" t="s">
         <v>144</v>
       </c>
@@ -8481,7 +8498,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:14" ns3:dyDescent="0.2">
       <c r="A486" t="s">
         <v>146</v>
       </c>
@@ -8501,7 +8518,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:14" ns3:dyDescent="0.2">
       <c r="A487" t="s">
         <v>148</v>
       </c>
@@ -8522,7 +8539,7 @@
       </c>
       <c r="N487" s="6"/>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:14" ns3:dyDescent="0.2">
       <c r="A488" t="s">
         <v>122</v>
       </c>
@@ -8542,7 +8559,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:14" ns3:dyDescent="0.2">
       <c r="A489" t="s">
         <v>150</v>
       </c>
@@ -8562,7 +8579,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:14" ns3:dyDescent="0.2">
       <c r="A490" t="s">
         <v>152</v>
       </c>
@@ -8579,7 +8596,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:14" ns3:dyDescent="0.2">
       <c r="A491" t="s">
         <v>153</v>
       </c>
@@ -8596,7 +8613,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="493" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:14" ht="16" ns3:dyDescent="0.2">
       <c r="A493" s="2" t="s">
         <v>0</v>
       </c>
@@ -8604,7 +8621,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:14" ns3:dyDescent="0.2">
       <c r="A494" t="s">
         <v>1</v>
       </c>
@@ -8612,7 +8629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:14" ns3:dyDescent="0.2">
       <c r="A495" t="s">
         <v>3</v>
       </c>
@@ -8620,7 +8637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:14" ns3:dyDescent="0.2">
       <c r="A496" t="s">
         <v>5</v>
       </c>
@@ -8628,7 +8645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11" ns3:dyDescent="0.2">
       <c r="A497" t="s">
         <v>6</v>
       </c>
@@ -8636,7 +8653,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11" ns3:dyDescent="0.2">
       <c r="A498" t="s">
         <v>7</v>
       </c>
@@ -8644,7 +8661,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11" ns3:dyDescent="0.2">
       <c r="A499" t="s">
         <v>9</v>
       </c>
@@ -8652,12 +8669,12 @@
         <v>187</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11" ns3:dyDescent="0.2">
       <c r="A500" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11" ns3:dyDescent="0.2">
       <c r="A501" t="s">
         <v>11</v>
       </c>
@@ -8680,7 +8697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11" ns3:dyDescent="0.2">
       <c r="A502" t="s">
         <v>163</v>
       </c>
@@ -8700,7 +8717,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11" ns3:dyDescent="0.2">
       <c r="A503" t="s">
         <v>61</v>
       </c>
@@ -8720,7 +8737,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11" ns3:dyDescent="0.2">
       <c r="A504" t="s">
         <v>55</v>
       </c>
@@ -8740,7 +8757,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:11" ns3:dyDescent="0.2">
       <c r="A505" t="s">
         <v>59</v>
       </c>
@@ -8760,7 +8777,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:11" ns3:dyDescent="0.2">
       <c r="A506" t="s">
         <v>188</v>
       </c>
@@ -8780,7 +8797,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:11" ns3:dyDescent="0.2">
       <c r="A507" t="s">
         <v>189</v>
       </c>
@@ -8800,7 +8817,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:11" ns3:dyDescent="0.2">
       <c r="A508" t="s">
         <v>45</v>
       </c>
@@ -8820,7 +8837,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:11" ns3:dyDescent="0.2">
       <c r="A509" t="s">
         <v>122</v>
       </c>
@@ -8840,7 +8857,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:11" ns3:dyDescent="0.2">
       <c r="A510" t="s">
         <v>190</v>
       </c>
@@ -8860,7 +8877,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:11" ns3:dyDescent="0.2">
       <c r="A511" t="s">
         <v>193</v>
       </c>
@@ -8880,7 +8897,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:11" ns3:dyDescent="0.2">
       <c r="A512" t="s">
         <v>164</v>
       </c>
@@ -8901,7 +8918,7 @@
       </c>
       <c r="K512" s="4"/>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11" ns3:dyDescent="0.2">
       <c r="A513" t="s">
         <v>191</v>
       </c>
@@ -8921,7 +8938,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:11" ns3:dyDescent="0.2">
       <c r="A514" t="s">
         <v>191</v>
       </c>
@@ -8941,7 +8958,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11" ns3:dyDescent="0.2">
       <c r="A515" t="s">
         <v>150</v>
       </c>
@@ -8961,7 +8978,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11" ns3:dyDescent="0.2">
       <c r="A516" t="s">
         <v>150</v>
       </c>
@@ -8981,7 +8998,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11" ns3:dyDescent="0.2">
       <c r="A517" t="s">
         <v>150</v>
       </c>
@@ -9001,7 +9018,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:11" ns3:dyDescent="0.2">
       <c r="A518" t="s">
         <v>195</v>
       </c>
@@ -9022,7 +9039,7 @@
       </c>
       <c r="K518" s="4"/>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:11" ns3:dyDescent="0.2">
       <c r="A519" t="s">
         <v>195</v>
       </c>
@@ -9043,7 +9060,7 @@
       </c>
       <c r="K519" s="4"/>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:11" ns3:dyDescent="0.2">
       <c r="A520" t="s">
         <v>197</v>
       </c>
@@ -9064,7 +9081,7 @@
       </c>
       <c r="K520" s="4"/>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11" ns3:dyDescent="0.2">
       <c r="A521" t="s">
         <v>197</v>
       </c>
@@ -9084,7 +9101,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="523" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A523" s="2" t="s">
         <v>0</v>
       </c>
@@ -9092,7 +9109,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:11" ns3:dyDescent="0.2">
       <c r="A524" t="s">
         <v>1</v>
       </c>
@@ -9100,7 +9117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:11" ns3:dyDescent="0.2">
       <c r="A525" t="s">
         <v>3</v>
       </c>
@@ -9108,7 +9125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:11" ns3:dyDescent="0.2">
       <c r="A526" t="s">
         <v>5</v>
       </c>
@@ -9116,7 +9133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:11" ht="16" ns3:dyDescent="0.2">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -9124,7 +9141,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:11" ns3:dyDescent="0.2">
       <c r="A528" t="s">
         <v>7</v>
       </c>
@@ -9132,12 +9149,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="529" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A529" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:6" ns3:dyDescent="0.2">
       <c r="A530" t="s">
         <v>11</v>
       </c>
@@ -9157,7 +9174,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="531" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A531" s="9" t="s">
         <v>300</v>
       </c>
@@ -9177,7 +9194,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:6" ns3:dyDescent="0.2">
       <c r="A532" t="s">
         <v>57</v>
       </c>
@@ -9197,7 +9214,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:6" ns3:dyDescent="0.2">
       <c r="A533" t="s">
         <v>52</v>
       </c>
@@ -9217,7 +9234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:6" ns3:dyDescent="0.2">
       <c r="A534" t="s">
         <v>59</v>
       </c>
@@ -9237,7 +9254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:6" ns3:dyDescent="0.2">
       <c r="A535" t="s">
         <v>294</v>
       </c>
@@ -9257,7 +9274,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:6" ns3:dyDescent="0.2">
       <c r="A536" t="s">
         <v>61</v>
       </c>
@@ -9277,7 +9294,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="537" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A537" s="9" t="s">
         <v>278</v>
       </c>
@@ -9297,7 +9314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="539" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A539" s="2" t="s">
         <v>0</v>
       </c>
@@ -9305,7 +9322,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:6" ns3:dyDescent="0.2">
       <c r="A540" t="s">
         <v>1</v>
       </c>
@@ -9313,7 +9330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:6" ns3:dyDescent="0.2">
       <c r="A541" t="s">
         <v>3</v>
       </c>
@@ -9321,7 +9338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:6" ns3:dyDescent="0.2">
       <c r="A542" t="s">
         <v>5</v>
       </c>
@@ -9329,7 +9346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A543" t="s">
         <v>6</v>
       </c>
@@ -9337,7 +9354,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:6" ns3:dyDescent="0.2">
       <c r="A544" t="s">
         <v>7</v>
       </c>
@@ -9345,7 +9362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:6" ns3:dyDescent="0.2">
       <c r="A545" t="s">
         <v>9</v>
       </c>
@@ -9353,12 +9370,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:6" ns3:dyDescent="0.2">
       <c r="A546" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:6" ns3:dyDescent="0.2">
       <c r="A547" t="s">
         <v>11</v>
       </c>
@@ -9378,7 +9395,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="548" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A548" t="s">
         <v>278</v>
       </c>
@@ -9398,7 +9415,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:6" ns3:dyDescent="0.2">
       <c r="A549" t="s">
         <v>112</v>
       </c>
@@ -9418,7 +9435,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:6" ns3:dyDescent="0.2">
       <c r="A550" t="s">
         <v>45</v>
       </c>
@@ -9438,7 +9455,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:6" ns3:dyDescent="0.2">
       <c r="A551" t="s">
         <v>199</v>
       </c>
@@ -9458,7 +9475,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:6" ns3:dyDescent="0.2">
       <c r="A552" t="s">
         <v>115</v>
       </c>
@@ -9478,7 +9495,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:6" ns3:dyDescent="0.2">
       <c r="A553" t="s">
         <v>116</v>
       </c>
@@ -9498,7 +9515,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:6" ns3:dyDescent="0.2">
       <c r="A554" t="s">
         <v>117</v>
       </c>
@@ -9518,7 +9535,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:6" ns3:dyDescent="0.2">
       <c r="A555" t="s">
         <v>43</v>
       </c>
@@ -9538,7 +9555,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:6" ns3:dyDescent="0.2">
       <c r="A556" t="s">
         <v>41</v>
       </c>
@@ -9558,7 +9575,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:6" ns3:dyDescent="0.2">
       <c r="A557" t="s">
         <v>118</v>
       </c>
@@ -9578,7 +9595,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:6" ns3:dyDescent="0.2">
       <c r="A558" t="s">
         <v>15</v>
       </c>
@@ -9598,7 +9615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:6" ns3:dyDescent="0.2">
       <c r="A559" t="s">
         <v>39</v>
       </c>
@@ -9618,7 +9635,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:6" ns3:dyDescent="0.2">
       <c r="A560" t="s">
         <v>119</v>
       </c>
@@ -9638,7 +9655,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:6" ns3:dyDescent="0.2">
       <c r="A561" t="s">
         <v>63</v>
       </c>
@@ -9658,7 +9675,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:6" ns3:dyDescent="0.2">
       <c r="A562" t="s">
         <v>85</v>
       </c>
@@ -9678,7 +9695,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:6" ns3:dyDescent="0.2">
       <c r="A563" t="s">
         <v>120</v>
       </c>
@@ -9698,7 +9715,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:6" ns3:dyDescent="0.2">
       <c r="A564" t="s">
         <v>122</v>
       </c>
@@ -9718,7 +9735,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="566" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A566" s="2" t="s">
         <v>0</v>
       </c>
@@ -9726,7 +9743,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:6" ns3:dyDescent="0.2">
       <c r="A567" t="s">
         <v>1</v>
       </c>
@@ -9734,7 +9751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:6" ns3:dyDescent="0.2">
       <c r="A568" t="s">
         <v>3</v>
       </c>
@@ -9742,7 +9759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:6" ns3:dyDescent="0.2">
       <c r="A569" t="s">
         <v>5</v>
       </c>
@@ -9750,7 +9767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:6" ns3:dyDescent="0.2">
       <c r="A570" t="s">
         <v>6</v>
       </c>
@@ -9758,7 +9775,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:6" ns3:dyDescent="0.2">
       <c r="A571" t="s">
         <v>7</v>
       </c>
@@ -9766,7 +9783,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:6" ns3:dyDescent="0.2">
       <c r="A572" t="s">
         <v>9</v>
       </c>
@@ -9774,12 +9791,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:6" ns3:dyDescent="0.2">
       <c r="A573" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:6" ns3:dyDescent="0.2">
       <c r="A574" t="s">
         <v>11</v>
       </c>
@@ -9799,7 +9816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:6" ns3:dyDescent="0.2">
       <c r="A575" t="s">
         <v>199</v>
       </c>
@@ -9819,7 +9836,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:6" ns3:dyDescent="0.2">
       <c r="A576" t="s">
         <v>124</v>
       </c>
@@ -9839,7 +9856,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:7" ns3:dyDescent="0.2">
       <c r="A577" t="s">
         <v>55</v>
       </c>
@@ -9859,7 +9876,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:7" ns3:dyDescent="0.2">
       <c r="A578" t="s">
         <v>61</v>
       </c>
@@ -9879,7 +9896,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:7" ns3:dyDescent="0.2">
       <c r="A579" t="s">
         <v>45</v>
       </c>
@@ -9899,7 +9916,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:7" ns3:dyDescent="0.2">
       <c r="A580" t="s">
         <v>125</v>
       </c>
@@ -9919,7 +9936,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:7" ns3:dyDescent="0.2">
       <c r="A581" t="s">
         <v>127</v>
       </c>
@@ -9939,7 +9956,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:7" ns3:dyDescent="0.2">
       <c r="A582" t="s">
         <v>112</v>
       </c>
@@ -9959,7 +9976,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:7" ns3:dyDescent="0.2">
       <c r="A583" t="s">
         <v>129</v>
       </c>
@@ -9979,7 +9996,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:7" ns3:dyDescent="0.2">
       <c r="A584" t="s">
         <v>122</v>
       </c>
@@ -10000,7 +10017,7 @@
       </c>
       <c r="G584" s="4"/>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:7" ns3:dyDescent="0.2">
       <c r="A585" t="s">
         <v>200</v>
       </c>
@@ -10020,7 +10037,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="587" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A587" s="2" t="s">
         <v>0</v>
       </c>
@@ -10028,15 +10045,17 @@
         <v>200</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:7" ns3:dyDescent="0.2">
       <c r="A588" t="s">
         <v>1</v>
       </c>
-      <c r="B588" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity). Preserve the original rounded anhydrous LiOH dose, precursor, output and energy boundary. Correct battery-grade monohydrate mass and add its water of crystallisation to the existing air emission. Existing reaction-water baseline is not validated by this change. NCA source includes 0.04 kg oxygen and 0.00024 m3 water; this workbook omits that oxygen and repeats the NMC811 water value. Those inherited reaction discrepancies need a separate correction. No complete reaction or whole-cell validation is claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" spans="1:7" ns3:dyDescent="0.2">
       <c r="A589" t="s">
         <v>3</v>
       </c>
@@ -10044,7 +10063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:7" ns3:dyDescent="0.2">
       <c r="A590" t="s">
         <v>5</v>
       </c>
@@ -10052,7 +10071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:7" ns3:dyDescent="0.2">
       <c r="A591" t="s">
         <v>6</v>
       </c>
@@ -10060,7 +10079,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:7" ns3:dyDescent="0.2">
       <c r="A592" t="s">
         <v>7</v>
       </c>
@@ -10068,7 +10087,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:7" ns3:dyDescent="0.2">
       <c r="A593" t="s">
         <v>9</v>
       </c>
@@ -10076,12 +10095,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:7" ns3:dyDescent="0.2">
       <c r="A594" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:7" ns3:dyDescent="0.2">
       <c r="A595" t="s">
         <v>11</v>
       </c>
@@ -10103,8 +10122,13 @@
       <c r="G595" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" spans="1:7" ns3:dyDescent="0.2">
       <c r="A596" t="s">
         <v>200</v>
       </c>
@@ -10124,7 +10148,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:7" ns3:dyDescent="0.2">
       <c r="A597" t="s">
         <v>124</v>
       </c>
@@ -10144,7 +10168,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:7" ns3:dyDescent="0.2">
       <c r="A598" t="s">
         <v>132</v>
       </c>
@@ -10164,7 +10188,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:7" ns3:dyDescent="0.2">
       <c r="A599" t="s">
         <v>61</v>
       </c>
@@ -10184,7 +10208,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:7" ns3:dyDescent="0.2">
       <c r="A600" t="s">
         <v>55</v>
       </c>
@@ -10204,7 +10228,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:7" ns3:dyDescent="0.2">
       <c r="A601" t="s">
         <v>45</v>
       </c>
@@ -10224,12 +10248,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:7" ns3:dyDescent="0.2">
       <c r="A602" t="s">
         <v>276</v>
       </c>
       <c r="B602" s="3">
-        <v>0.25</v>
+        <v>0.4380715747275233</v>
       </c>
       <c r="C602" t="s">
         <v>8</v>
@@ -10243,8 +10267,13 @@
       <c r="G602" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1: preserve 0.25 kg anhydrous LiOH equivalent per kg oxide; purchase 0.43807157472752328 kg LiOH.H2O = 0.25 * 41.962 / 23.947. Atomic masses Li=6.94, H=1.008, O=15.999 g/mol. No additional yield or excess-lithium factor. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" spans="1:7" ns3:dyDescent="0.2">
       <c r="A603" t="s">
         <v>201</v>
       </c>
@@ -10264,7 +10293,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:7" ns3:dyDescent="0.2">
       <c r="A604" t="s">
         <v>122</v>
       </c>
@@ -10284,12 +10313,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:7" ns3:dyDescent="0.2">
       <c r="A605" t="s">
         <v>137</v>
       </c>
       <c r="B605" s="3">
-        <v>1.9562E-4</v>
+        <v>0.0003836915747275233</v>
       </c>
       <c r="C605" t="s">
         <v>138</v>
@@ -10300,11 +10329,16 @@
       <c r="F605" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Hydrate-basis correction v1: retained inherited 0.00019562 m3 reaction-water baseline plus 0.18807157472752328 kg water of crystallisation / 1000 kg/m3. Assume bound water exits to air during calcination through the existing Water flow. This closes the hydration increment only; original reaction-water/oxygen balance remains unresolved. Crenna et al. 2021, doi:10.1016/j.resconrec.2021.105619, supplementary workbook, NMC811 J191-J196 and NCA J191-J196; Kelly et al. 2021, doi:10.1016/j.resconrec.2021.105762 (LiOH.H2O product identity).</t>
+        </is>
+      </c>
+    </row>
+    <row r="606" spans="1:7" ns3:dyDescent="0.2">
       <c r="G606" s="4"/>
     </row>
-    <row r="607" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A607" s="2" t="s">
         <v>0</v>
       </c>
@@ -10312,7 +10346,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:7" ns3:dyDescent="0.2">
       <c r="A608" t="s">
         <v>1</v>
       </c>
@@ -10320,7 +10354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:7" ns3:dyDescent="0.2">
       <c r="A609" t="s">
         <v>3</v>
       </c>
@@ -10328,7 +10362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:7" ns3:dyDescent="0.2">
       <c r="A610" t="s">
         <v>5</v>
       </c>
@@ -10336,7 +10370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:7" ns3:dyDescent="0.2">
       <c r="A611" t="s">
         <v>6</v>
       </c>
@@ -10344,7 +10378,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:7" ns3:dyDescent="0.2">
       <c r="A612" t="s">
         <v>7</v>
       </c>
@@ -10352,7 +10386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:7" ns3:dyDescent="0.2">
       <c r="A613" t="s">
         <v>9</v>
       </c>
@@ -10360,12 +10394,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:7" ns3:dyDescent="0.2">
       <c r="A614" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:7" ns3:dyDescent="0.2">
       <c r="A615" t="s">
         <v>11</v>
       </c>
@@ -10388,7 +10422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:7" ns3:dyDescent="0.2">
       <c r="A616" t="s">
         <v>201</v>
       </c>
@@ -10408,7 +10442,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:7" ns3:dyDescent="0.2">
       <c r="A617" t="s">
         <v>132</v>
       </c>
@@ -10428,7 +10462,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:7" ns3:dyDescent="0.2">
       <c r="A618" t="s">
         <v>55</v>
       </c>
@@ -10448,7 +10482,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:7" ns3:dyDescent="0.2">
       <c r="A619" t="s">
         <v>124</v>
       </c>
@@ -10468,7 +10502,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:7" ns3:dyDescent="0.2">
       <c r="A620" t="s">
         <v>61</v>
       </c>
@@ -10488,7 +10522,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:7" ns3:dyDescent="0.2">
       <c r="A621" t="s">
         <v>112</v>
       </c>
@@ -10508,7 +10542,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:7" ns3:dyDescent="0.2">
       <c r="A622" t="s">
         <v>141</v>
       </c>
@@ -10528,7 +10562,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:7" ns3:dyDescent="0.2">
       <c r="A623" t="s">
         <v>273</v>
       </c>
@@ -10548,7 +10582,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:7" ns3:dyDescent="0.2">
       <c r="A624" t="s">
         <v>144</v>
       </c>
@@ -10568,7 +10602,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:7" ns3:dyDescent="0.2">
       <c r="A625" t="s">
         <v>202</v>
       </c>
@@ -10588,7 +10622,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:7" ns3:dyDescent="0.2">
       <c r="A626" t="s">
         <v>148</v>
       </c>
@@ -10608,7 +10642,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:7" ns3:dyDescent="0.2">
       <c r="A627" t="s">
         <v>122</v>
       </c>
@@ -10628,7 +10662,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:7" ns3:dyDescent="0.2">
       <c r="A628" t="s">
         <v>150</v>
       </c>
@@ -10648,7 +10682,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:7" ns3:dyDescent="0.2">
       <c r="A629" t="s">
         <v>152</v>
       </c>
@@ -10665,7 +10699,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:7" ns3:dyDescent="0.2">
       <c r="A630" t="s">
         <v>153</v>
       </c>
@@ -10682,7 +10716,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="632" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A632" s="2" t="s">
         <v>0</v>
       </c>
@@ -10690,7 +10724,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:7" ns3:dyDescent="0.2">
       <c r="A633" t="s">
         <v>1</v>
       </c>
@@ -10698,7 +10732,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:7" ns3:dyDescent="0.2">
       <c r="A634" t="s">
         <v>3</v>
       </c>
@@ -10706,7 +10740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:7" ns3:dyDescent="0.2">
       <c r="A635" t="s">
         <v>5</v>
       </c>
@@ -10714,7 +10748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:7" ns3:dyDescent="0.2">
       <c r="A636" t="s">
         <v>6</v>
       </c>
@@ -10722,7 +10756,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:7" ns3:dyDescent="0.2">
       <c r="A637" t="s">
         <v>7</v>
       </c>
@@ -10730,12 +10764,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="638" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A638" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:7" ns3:dyDescent="0.2">
       <c r="A639" t="s">
         <v>11</v>
       </c>
@@ -10755,7 +10789,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="640" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A640" s="7" t="str">
         <f>B632</f>
         <v>market for battery, Li-ion, LFP, rechargeable, prismatic</v>
@@ -10777,7 +10811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="641" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A641" s="7" t="s">
         <v>293</v>
       </c>
@@ -10797,7 +10831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="642" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A642" s="9" t="s">
         <v>295</v>
       </c>
@@ -10817,7 +10851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="644" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A644" s="2" t="s">
         <v>0</v>
       </c>
@@ -10825,7 +10859,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:6" ns3:dyDescent="0.2">
       <c r="A645" t="s">
         <v>1</v>
       </c>
@@ -10833,7 +10867,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:6" ns3:dyDescent="0.2">
       <c r="A646" t="s">
         <v>3</v>
       </c>
@@ -10841,7 +10875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:6" ns3:dyDescent="0.2">
       <c r="A647" t="s">
         <v>5</v>
       </c>
@@ -10849,7 +10883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:6" ns3:dyDescent="0.2">
       <c r="A648" t="s">
         <v>6</v>
       </c>
@@ -10857,7 +10891,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:6" ns3:dyDescent="0.2">
       <c r="A649" t="s">
         <v>7</v>
       </c>
@@ -10865,12 +10899,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="650" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A650" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:6" ns3:dyDescent="0.2">
       <c r="A651" t="s">
         <v>11</v>
       </c>
@@ -10890,7 +10924,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="652" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A652" s="7" t="s">
         <v>293</v>
       </c>
@@ -10910,7 +10944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:6" ns3:dyDescent="0.2">
       <c r="A653" t="s">
         <v>57</v>
       </c>
@@ -10930,7 +10964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="654" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:6" ht="14" customHeight="1" ns3:dyDescent="0.2">
       <c r="A654" t="s">
         <v>52</v>
       </c>
@@ -10950,7 +10984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:6" ns3:dyDescent="0.2">
       <c r="A655" t="s">
         <v>59</v>
       </c>
@@ -10970,7 +11004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:6" ns3:dyDescent="0.2">
       <c r="A656" t="s">
         <v>294</v>
       </c>
@@ -10990,7 +11024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="657" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:10" ns3:dyDescent="0.2">
       <c r="A657" t="s">
         <v>61</v>
       </c>
@@ -11010,7 +11044,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="658" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A658" s="7" t="s">
         <v>279</v>
       </c>
@@ -11030,7 +11064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="660" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A660" s="2" t="s">
         <v>0</v>
       </c>
@@ -11038,7 +11072,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="661" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:10" ns3:dyDescent="0.2">
       <c r="A661" t="s">
         <v>1</v>
       </c>
@@ -11046,7 +11080,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="662" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:10" ns3:dyDescent="0.2">
       <c r="A662" t="s">
         <v>3</v>
       </c>
@@ -11054,7 +11088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="663" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:10" ns3:dyDescent="0.2">
       <c r="A663" t="s">
         <v>5</v>
       </c>
@@ -11062,7 +11096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="664" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:10" ns3:dyDescent="0.2">
       <c r="A664" t="s">
         <v>6</v>
       </c>
@@ -11070,7 +11104,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="665" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:10" ns3:dyDescent="0.2">
       <c r="A665" t="s">
         <v>7</v>
       </c>
@@ -11078,12 +11112,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="666" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A666" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="667" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:10" ns3:dyDescent="0.2">
       <c r="A667" t="s">
         <v>11</v>
       </c>
@@ -11115,7 +11149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A668" s="7" t="s">
         <v>279</v>
       </c>
@@ -11138,7 +11172,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="669" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:10" ns3:dyDescent="0.2">
       <c r="A669" t="s">
         <v>207</v>
       </c>
@@ -11158,7 +11192,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="670" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:10" ns3:dyDescent="0.2">
       <c r="A670" t="s">
         <v>209</v>
       </c>
@@ -11178,7 +11212,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="671" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:10" ns3:dyDescent="0.2">
       <c r="A671" t="s">
         <v>210</v>
       </c>
@@ -11198,7 +11232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="672" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:10" ns3:dyDescent="0.2">
       <c r="A672" t="s">
         <v>211</v>
       </c>
@@ -11218,7 +11252,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="673" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:10" ns3:dyDescent="0.2">
       <c r="A673" t="s">
         <v>212</v>
       </c>
@@ -11238,7 +11272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="674" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:10" ns3:dyDescent="0.2">
       <c r="A674" t="s">
         <v>119</v>
       </c>
@@ -11261,7 +11295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="675" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:10" ns3:dyDescent="0.2">
       <c r="A675" t="s">
         <v>213</v>
       </c>
@@ -11284,7 +11318,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="676" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:10" ns3:dyDescent="0.2">
       <c r="A676" t="s">
         <v>215</v>
       </c>
@@ -11307,7 +11341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="677" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:10" ns3:dyDescent="0.2">
       <c r="A677" t="s">
         <v>45</v>
       </c>
@@ -11333,7 +11367,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="678" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:10" ns3:dyDescent="0.2">
       <c r="A678" t="s">
         <v>112</v>
       </c>
@@ -11356,7 +11390,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="681" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A681" s="2" t="s">
         <v>0</v>
       </c>
@@ -11364,7 +11398,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="682" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:10" ns3:dyDescent="0.2">
       <c r="A682" t="s">
         <v>1</v>
       </c>
@@ -11372,7 +11406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:10" ns3:dyDescent="0.2">
       <c r="A683" t="s">
         <v>3</v>
       </c>
@@ -11380,7 +11414,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="684" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:10" ns3:dyDescent="0.2">
       <c r="A684" t="s">
         <v>5</v>
       </c>
@@ -11388,7 +11422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="685" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:10" ns3:dyDescent="0.2">
       <c r="A685" t="s">
         <v>6</v>
       </c>
@@ -11396,7 +11430,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="686" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:10" ns3:dyDescent="0.2">
       <c r="A686" t="s">
         <v>7</v>
       </c>
@@ -11404,7 +11438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="687" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:10" ns3:dyDescent="0.2">
       <c r="A687" t="s">
         <v>219</v>
       </c>
@@ -11412,12 +11446,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="688" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:10" ht="16" ns3:dyDescent="0.2">
       <c r="A688" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:8" ns3:dyDescent="0.2">
       <c r="A689" t="s">
         <v>11</v>
       </c>
@@ -11443,7 +11477,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:8" ns3:dyDescent="0.2">
       <c r="A690" t="s">
         <v>209</v>
       </c>
@@ -11463,7 +11497,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:8" ns3:dyDescent="0.2">
       <c r="A691" t="s">
         <v>115</v>
       </c>
@@ -11489,7 +11523,7 @@
         <v>0.86185933408155613</v>
       </c>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:8" ns3:dyDescent="0.2">
       <c r="A692" t="s">
         <v>125</v>
       </c>
@@ -11512,7 +11546,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:8" ns3:dyDescent="0.2">
       <c r="A693" t="s">
         <v>155</v>
       </c>
@@ -11538,7 +11572,7 @@
         <v>3.3516751880949401E-2</v>
       </c>
     </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:8" ns3:dyDescent="0.2">
       <c r="A694" t="s">
         <v>223</v>
       </c>
@@ -11561,7 +11595,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="696" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A696" s="2" t="s">
         <v>0</v>
       </c>
@@ -11569,7 +11603,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:8" ns3:dyDescent="0.2">
       <c r="A697" t="s">
         <v>1</v>
       </c>
@@ -11577,7 +11611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:8" ns3:dyDescent="0.2">
       <c r="A698" t="s">
         <v>3</v>
       </c>
@@ -11585,7 +11619,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:8" ns3:dyDescent="0.2">
       <c r="A699" t="s">
         <v>5</v>
       </c>
@@ -11593,7 +11627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:8" ns3:dyDescent="0.2">
       <c r="A700" t="s">
         <v>6</v>
       </c>
@@ -11601,7 +11635,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:8" ns3:dyDescent="0.2">
       <c r="A701" t="s">
         <v>7</v>
       </c>
@@ -11609,7 +11643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:8" ns3:dyDescent="0.2">
       <c r="A702" t="s">
         <v>219</v>
       </c>
@@ -11617,12 +11651,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="703" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A703" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:8" ns3:dyDescent="0.2">
       <c r="A704" t="s">
         <v>11</v>
       </c>
@@ -11645,7 +11679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="705" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:7" ns3:dyDescent="0.2">
       <c r="A705" t="s">
         <v>210</v>
       </c>
@@ -11665,7 +11699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="706" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:7" ns3:dyDescent="0.2">
       <c r="A706" t="s">
         <v>226</v>
       </c>
@@ -11688,7 +11722,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="707" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:7" ns3:dyDescent="0.2">
       <c r="A707" t="s">
         <v>39</v>
       </c>
@@ -11711,7 +11745,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="709" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A709" s="2" t="s">
         <v>0</v>
       </c>
@@ -11719,7 +11753,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="710" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:7" ns3:dyDescent="0.2">
       <c r="A710" t="s">
         <v>1</v>
       </c>
@@ -11727,7 +11761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="711" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:7" ns3:dyDescent="0.2">
       <c r="A711" t="s">
         <v>3</v>
       </c>
@@ -11735,7 +11769,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="712" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:7" ns3:dyDescent="0.2">
       <c r="A712" t="s">
         <v>5</v>
       </c>
@@ -11743,7 +11777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="713" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:7" ns3:dyDescent="0.2">
       <c r="A713" t="s">
         <v>6</v>
       </c>
@@ -11751,7 +11785,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="714" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:7" ns3:dyDescent="0.2">
       <c r="A714" t="s">
         <v>7</v>
       </c>
@@ -11759,7 +11793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="715" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:7" ns3:dyDescent="0.2">
       <c r="A715" t="s">
         <v>219</v>
       </c>
@@ -11767,12 +11801,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="716" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A716" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="717" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:7" ns3:dyDescent="0.2">
       <c r="A717" t="s">
         <v>11</v>
       </c>
@@ -11795,7 +11829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="718" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:7" ns3:dyDescent="0.2">
       <c r="A718" t="s">
         <v>207</v>
       </c>
@@ -11815,7 +11849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="719" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:7" ns3:dyDescent="0.2">
       <c r="A719" t="s">
         <v>229</v>
       </c>
@@ -11835,7 +11869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="720" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:7" ns3:dyDescent="0.2">
       <c r="A720" t="s">
         <v>129</v>
       </c>
@@ -11858,7 +11892,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="721" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:7" ns3:dyDescent="0.2">
       <c r="A721" t="s">
         <v>125</v>
       </c>
@@ -11881,7 +11915,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="722" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:7" ns3:dyDescent="0.2">
       <c r="A722" t="s">
         <v>127</v>
       </c>
@@ -11904,7 +11938,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="724" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A724" s="2" t="s">
         <v>0</v>
       </c>
@@ -11912,7 +11946,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="725" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:7" ns3:dyDescent="0.2">
       <c r="A725" t="s">
         <v>1</v>
       </c>
@@ -11920,7 +11954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="726" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:7" ns3:dyDescent="0.2">
       <c r="A726" t="s">
         <v>3</v>
       </c>
@@ -11928,7 +11962,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="727" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:7" ns3:dyDescent="0.2">
       <c r="A727" t="s">
         <v>5</v>
       </c>
@@ -11936,7 +11970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="728" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:7" ns3:dyDescent="0.2">
       <c r="A728" t="s">
         <v>6</v>
       </c>
@@ -11944,7 +11978,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="729" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:7" ns3:dyDescent="0.2">
       <c r="A729" t="s">
         <v>7</v>
       </c>
@@ -11952,7 +11986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="730" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:7" ns3:dyDescent="0.2">
       <c r="A730" t="s">
         <v>219</v>
       </c>
@@ -11960,12 +11994,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="731" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A731" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="732" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:7" ns3:dyDescent="0.2">
       <c r="A732" t="s">
         <v>11</v>
       </c>
@@ -11988,7 +12022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="733" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:7" ns3:dyDescent="0.2">
       <c r="A733" t="s">
         <v>212</v>
       </c>
@@ -12008,7 +12042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="734" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:7" ns3:dyDescent="0.2">
       <c r="A734" t="s">
         <v>164</v>
       </c>
@@ -12031,7 +12065,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="735" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:7" ns3:dyDescent="0.2">
       <c r="A735" t="s">
         <v>166</v>
       </c>
@@ -12054,7 +12088,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="737" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A737" s="2" t="s">
         <v>0</v>
       </c>
@@ -12062,7 +12096,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="738" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:7" ns3:dyDescent="0.2">
       <c r="A738" t="s">
         <v>1</v>
       </c>
@@ -12070,7 +12104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="739" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:7" ns3:dyDescent="0.2">
       <c r="A739" t="s">
         <v>3</v>
       </c>
@@ -12078,7 +12112,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="740" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:7" ns3:dyDescent="0.2">
       <c r="A740" t="s">
         <v>5</v>
       </c>
@@ -12086,7 +12120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="741" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:7" ns3:dyDescent="0.2">
       <c r="A741" t="s">
         <v>6</v>
       </c>
@@ -12094,7 +12128,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="742" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:7" ns3:dyDescent="0.2">
       <c r="A742" t="s">
         <v>7</v>
       </c>
@@ -12102,7 +12136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="743" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:7" ns3:dyDescent="0.2">
       <c r="A743" t="s">
         <v>219</v>
       </c>
@@ -12110,12 +12144,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="744" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A744" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="745" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:7" ns3:dyDescent="0.2">
       <c r="A745" t="s">
         <v>11</v>
       </c>
@@ -12138,7 +12172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="746" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:7" ns3:dyDescent="0.2">
       <c r="A746" t="s">
         <v>230</v>
       </c>
@@ -12158,7 +12192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="747" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:7" ns3:dyDescent="0.2">
       <c r="A747" t="s">
         <v>63</v>
       </c>
@@ -12181,7 +12215,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="748" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:7" ns3:dyDescent="0.2">
       <c r="A748" t="s">
         <v>231</v>
       </c>
@@ -12204,7 +12238,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="749" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:7" ns3:dyDescent="0.2">
       <c r="A749" t="s">
         <v>120</v>
       </c>
@@ -12227,7 +12261,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="751" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A751" s="2" t="s">
         <v>0</v>
       </c>
@@ -12235,7 +12269,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="752" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:7" ns3:dyDescent="0.2">
       <c r="A752" t="s">
         <v>1</v>
       </c>
@@ -12243,7 +12277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="753" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:7" ns3:dyDescent="0.2">
       <c r="A753" t="s">
         <v>3</v>
       </c>
@@ -12251,7 +12285,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="754" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:7" ns3:dyDescent="0.2">
       <c r="A754" t="s">
         <v>5</v>
       </c>
@@ -12259,7 +12293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:7" ns3:dyDescent="0.2">
       <c r="A755" t="s">
         <v>6</v>
       </c>
@@ -12267,7 +12301,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="756" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:7" ns3:dyDescent="0.2">
       <c r="A756" t="s">
         <v>7</v>
       </c>
@@ -12275,7 +12309,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="757" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:7" ns3:dyDescent="0.2">
       <c r="A757" t="s">
         <v>219</v>
       </c>
@@ -12283,12 +12317,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="758" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A758" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="759" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:7" ns3:dyDescent="0.2">
       <c r="A759" t="s">
         <v>11</v>
       </c>
@@ -12311,7 +12345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="760" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:7" ns3:dyDescent="0.2">
       <c r="A760" t="s">
         <v>211</v>
       </c>
@@ -12331,7 +12365,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="761" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:7" ns3:dyDescent="0.2">
       <c r="A761" t="s">
         <v>41</v>
       </c>
@@ -12354,7 +12388,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="762" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:7" ns3:dyDescent="0.2">
       <c r="A762" t="s">
         <v>43</v>
       </c>
@@ -12377,7 +12411,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="764" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A764" s="2" t="s">
         <v>0</v>
       </c>
@@ -12385,7 +12419,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="765" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:7" ns3:dyDescent="0.2">
       <c r="A765" t="s">
         <v>1</v>
       </c>
@@ -12393,7 +12427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="766" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:7" ns3:dyDescent="0.2">
       <c r="A766" t="s">
         <v>3</v>
       </c>
@@ -12401,7 +12435,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="767" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:7" ns3:dyDescent="0.2">
       <c r="A767" t="s">
         <v>5</v>
       </c>
@@ -12409,7 +12443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="768" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:7" ns3:dyDescent="0.2">
       <c r="A768" t="s">
         <v>6</v>
       </c>
@@ -12417,7 +12451,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="769" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:8" ns3:dyDescent="0.2">
       <c r="A769" t="s">
         <v>7</v>
       </c>
@@ -12425,7 +12459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="770" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:8" ns3:dyDescent="0.2">
       <c r="A770" t="s">
         <v>219</v>
       </c>
@@ -12433,12 +12467,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="771" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A771" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="772" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:8" ns3:dyDescent="0.2">
       <c r="A772" t="s">
         <v>11</v>
       </c>
@@ -12464,7 +12498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="773" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:8" ns3:dyDescent="0.2">
       <c r="A773" t="s">
         <v>233</v>
       </c>
@@ -12484,7 +12518,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="774" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:8" ns3:dyDescent="0.2">
       <c r="A774" t="s">
         <v>235</v>
       </c>
@@ -12504,7 +12538,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="775" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:8" ns3:dyDescent="0.2">
       <c r="A775" t="s">
         <v>236</v>
       </c>
@@ -12524,7 +12558,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="776" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:8" ns3:dyDescent="0.2">
       <c r="A776" t="s">
         <v>237</v>
       </c>
@@ -12544,7 +12578,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="777" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:8" ns3:dyDescent="0.2">
       <c r="A777" t="s">
         <v>229</v>
       </c>
@@ -12564,7 +12598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="778" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:8" ns3:dyDescent="0.2">
       <c r="A778" t="s">
         <v>122</v>
       </c>
@@ -12587,7 +12621,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="779" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:8" ns3:dyDescent="0.2">
       <c r="A779" t="s">
         <v>238</v>
       </c>
@@ -12610,7 +12644,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="780" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:8" ns3:dyDescent="0.2">
       <c r="A780" t="s">
         <v>240</v>
       </c>
@@ -12633,7 +12667,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="781" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:8" ns3:dyDescent="0.2">
       <c r="A781" t="s">
         <v>276</v>
       </c>
@@ -12656,7 +12690,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="782" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:8" ns3:dyDescent="0.2">
       <c r="A782" t="s">
         <v>242</v>
       </c>
@@ -12679,7 +12713,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="783" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:8" ns3:dyDescent="0.2">
       <c r="A783" t="s">
         <v>157</v>
       </c>
@@ -12702,7 +12736,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="785" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A785" s="2" t="s">
         <v>0</v>
       </c>
@@ -12710,7 +12744,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:6" ns3:dyDescent="0.2">
       <c r="A786" t="s">
         <v>1</v>
       </c>
@@ -12718,7 +12752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:6" ns3:dyDescent="0.2">
       <c r="A787" t="s">
         <v>3</v>
       </c>
@@ -12726,7 +12760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:6" ns3:dyDescent="0.2">
       <c r="A788" t="s">
         <v>5</v>
       </c>
@@ -12734,7 +12768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:6" ns3:dyDescent="0.2">
       <c r="A789" t="s">
         <v>6</v>
       </c>
@@ -12742,7 +12776,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:6" ns3:dyDescent="0.2">
       <c r="A790" t="s">
         <v>7</v>
       </c>
@@ -12750,7 +12784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:6" ns3:dyDescent="0.2">
       <c r="A791" t="s">
         <v>219</v>
       </c>
@@ -12758,12 +12792,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="792" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A792" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:6" ns3:dyDescent="0.2">
       <c r="A793" t="s">
         <v>11</v>
       </c>
@@ -12783,7 +12817,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:6" ns3:dyDescent="0.2">
       <c r="A794" t="s">
         <v>213</v>
       </c>
@@ -12803,7 +12837,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:6" ns3:dyDescent="0.2">
       <c r="A795" t="s">
         <v>244</v>
       </c>
@@ -12823,7 +12857,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:6" ns3:dyDescent="0.2">
       <c r="A796" t="s">
         <v>245</v>
       </c>
@@ -12843,7 +12877,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:6" ns3:dyDescent="0.2">
       <c r="A797" t="s">
         <v>246</v>
       </c>
@@ -12863,7 +12897,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="799" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:6" ht="16" ns3:dyDescent="0.2">
       <c r="A799" s="2" t="s">
         <v>0</v>
       </c>
@@ -12871,7 +12905,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:6" ns3:dyDescent="0.2">
       <c r="A800" t="s">
         <v>1</v>
       </c>
@@ -12879,7 +12913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="801" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:8" ns3:dyDescent="0.2">
       <c r="A801" t="s">
         <v>3</v>
       </c>
@@ -12887,7 +12921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="802" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:8" ns3:dyDescent="0.2">
       <c r="A802" t="s">
         <v>5</v>
       </c>
@@ -12895,7 +12929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="803" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:8" ns3:dyDescent="0.2">
       <c r="A803" t="s">
         <v>6</v>
       </c>
@@ -12903,7 +12937,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="804" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:8" ns3:dyDescent="0.2">
       <c r="A804" t="s">
         <v>7</v>
       </c>
@@ -12911,7 +12945,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="805" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:8" ns3:dyDescent="0.2">
       <c r="A805" t="s">
         <v>219</v>
       </c>
@@ -12919,12 +12953,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="806" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A806" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="807" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:8" ns3:dyDescent="0.2">
       <c r="A807" t="s">
         <v>11</v>
       </c>
@@ -12950,7 +12984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="808" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:8" ns3:dyDescent="0.2">
       <c r="A808" t="s">
         <v>244</v>
       </c>
@@ -12970,7 +13004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="809" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:8" ns3:dyDescent="0.2">
       <c r="A809" t="s">
         <v>248</v>
       </c>
@@ -12993,7 +13027,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="810" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:8" ns3:dyDescent="0.2">
       <c r="A810" t="s">
         <v>173</v>
       </c>
@@ -13016,7 +13050,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="811" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:8" ns3:dyDescent="0.2">
       <c r="A811" t="s">
         <v>35</v>
       </c>
@@ -13039,7 +13073,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="812" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:8" ns3:dyDescent="0.2">
       <c r="A812" t="s">
         <v>98</v>
       </c>
@@ -13062,7 +13096,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="813" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:8" ns3:dyDescent="0.2">
       <c r="A813" t="s">
         <v>250</v>
       </c>
@@ -13085,7 +13119,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="814" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:8" ns3:dyDescent="0.2">
       <c r="A814" t="s">
         <v>252</v>
       </c>
@@ -13108,7 +13142,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="815" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:8" ns3:dyDescent="0.2">
       <c r="A815" t="s">
         <v>85</v>
       </c>
@@ -13134,7 +13168,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="816" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:8" ns3:dyDescent="0.2">
       <c r="A816" t="s">
         <v>120</v>
       </c>
@@ -13157,7 +13191,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="817" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:8" ns3:dyDescent="0.2">
       <c r="A817" t="s">
         <v>39</v>
       </c>
@@ -13180,7 +13214,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="819" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A819" s="2" t="s">
         <v>0</v>
       </c>
@@ -13188,7 +13222,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="820" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:8" ns3:dyDescent="0.2">
       <c r="A820" t="s">
         <v>1</v>
       </c>
@@ -13196,7 +13230,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="821" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:8" ns3:dyDescent="0.2">
       <c r="A821" t="s">
         <v>3</v>
       </c>
@@ -13204,7 +13238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="822" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:8" ns3:dyDescent="0.2">
       <c r="A822" t="s">
         <v>5</v>
       </c>
@@ -13212,7 +13246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="823" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:8" ns3:dyDescent="0.2">
       <c r="A823" t="s">
         <v>6</v>
       </c>
@@ -13220,7 +13254,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="824" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:8" ns3:dyDescent="0.2">
       <c r="A824" t="s">
         <v>7</v>
       </c>
@@ -13228,7 +13262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="825" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:8" ns3:dyDescent="0.2">
       <c r="A825" t="s">
         <v>219</v>
       </c>
@@ -13236,12 +13270,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="826" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A826" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="827" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:8" ns3:dyDescent="0.2">
       <c r="A827" t="s">
         <v>11</v>
       </c>
@@ -13264,7 +13298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="828" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:8" ns3:dyDescent="0.2">
       <c r="A828" t="s">
         <v>245</v>
       </c>
@@ -13284,7 +13318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="829" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:8" ns3:dyDescent="0.2">
       <c r="A829" t="s">
         <v>248</v>
       </c>
@@ -13307,7 +13341,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="830" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:8" ns3:dyDescent="0.2">
       <c r="A830" t="s">
         <v>173</v>
       </c>
@@ -13330,7 +13364,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="831" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:8" ns3:dyDescent="0.2">
       <c r="A831" t="s">
         <v>39</v>
       </c>
@@ -13353,7 +13387,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="833" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A833" s="2" t="s">
         <v>0</v>
       </c>
@@ -13361,7 +13395,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="834" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:7" ns3:dyDescent="0.2">
       <c r="A834" t="s">
         <v>1</v>
       </c>
@@ -13369,7 +13403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="835" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:7" ns3:dyDescent="0.2">
       <c r="A835" t="s">
         <v>3</v>
       </c>
@@ -13377,7 +13411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="836" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:7" ns3:dyDescent="0.2">
       <c r="A836" t="s">
         <v>5</v>
       </c>
@@ -13385,7 +13419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="837" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:7" ns3:dyDescent="0.2">
       <c r="A837" t="s">
         <v>6</v>
       </c>
@@ -13393,7 +13427,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="838" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:7" ns3:dyDescent="0.2">
       <c r="A838" t="s">
         <v>7</v>
       </c>
@@ -13401,7 +13435,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="839" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:7" ns3:dyDescent="0.2">
       <c r="A839" t="s">
         <v>219</v>
       </c>
@@ -13409,12 +13443,12 @@
         <v>206</v>
       </c>
     </row>
-    <row r="840" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A840" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="841" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:7" ns3:dyDescent="0.2">
       <c r="A841" t="s">
         <v>11</v>
       </c>
@@ -13437,7 +13471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="842" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:7" ns3:dyDescent="0.2">
       <c r="A842" t="s">
         <v>246</v>
       </c>
@@ -13457,7 +13491,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="843" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:7" ns3:dyDescent="0.2">
       <c r="A843" t="s">
         <v>41</v>
       </c>
@@ -13480,7 +13514,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="844" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:7" ns3:dyDescent="0.2">
       <c r="A844" t="s">
         <v>50</v>
       </c>
@@ -13503,7 +13537,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="845" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:7" ns3:dyDescent="0.2">
       <c r="A845" t="s">
         <v>43</v>
       </c>
@@ -13526,7 +13560,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="847" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:7" ht="16" ns3:dyDescent="0.2">
       <c r="A847" s="2" t="s">
         <v>0</v>
       </c>
@@ -13534,7 +13568,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="848" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:7" ns3:dyDescent="0.2">
       <c r="A848" t="s">
         <v>3</v>
       </c>
@@ -13542,7 +13576,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="849" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:8" ns3:dyDescent="0.2">
       <c r="A849" t="s">
         <v>5</v>
       </c>
@@ -13550,7 +13584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="850" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:8" ns3:dyDescent="0.2">
       <c r="A850" t="s">
         <v>6</v>
       </c>
@@ -13558,7 +13592,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="851" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:8" ns3:dyDescent="0.2">
       <c r="A851" t="s">
         <v>13</v>
       </c>
@@ -13566,7 +13600,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="852" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:8" ns3:dyDescent="0.2">
       <c r="A852" t="s">
         <v>7</v>
       </c>
@@ -13574,12 +13608,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="853" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:8" ht="16" ns3:dyDescent="0.2">
       <c r="A853" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="854" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:8" ns3:dyDescent="0.2">
       <c r="A854" t="s">
         <v>11</v>
       </c>
@@ -13605,7 +13639,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="855" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:8" ns3:dyDescent="0.2">
       <c r="A855" t="s">
         <v>233</v>
       </c>
@@ -13625,7 +13659,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="856" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:8" ns3:dyDescent="0.2">
       <c r="A856" t="s">
         <v>256</v>
       </c>
@@ -13645,7 +13679,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="857" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:8" ns3:dyDescent="0.2">
       <c r="A857" t="s">
         <v>153</v>
       </c>
@@ -13665,7 +13699,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="858" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:8" ns3:dyDescent="0.2">
       <c r="A858" t="s">
         <v>223</v>
       </c>
@@ -13688,7 +13722,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="859" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:8" ns3:dyDescent="0.2">
       <c r="A859" t="s">
         <v>257</v>
       </c>
@@ -13711,7 +13745,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="860" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:8" ns3:dyDescent="0.2">
       <c r="A860" t="s">
         <v>259</v>
       </c>
@@ -13734,7 +13768,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="861" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:8" ns3:dyDescent="0.2">
       <c r="A861" t="s">
         <v>261</v>
       </c>
@@ -13757,7 +13791,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="862" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:8" ns3:dyDescent="0.2">
       <c r="A862" t="s">
         <v>263</v>
       </c>
@@ -13780,7 +13814,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="863" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:8" ns3:dyDescent="0.2">
       <c r="A863" t="s">
         <v>265</v>
       </c>
@@ -13803,7 +13837,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="864" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:8" ns3:dyDescent="0.2">
       <c r="A864" t="s">
         <v>157</v>
       </c>
@@ -13826,7 +13860,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:8" ns3:dyDescent="0.2">
       <c r="A865" t="s">
         <v>45</v>
       </c>
@@ -13849,7 +13883,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="866" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:8" ns3:dyDescent="0.2">
       <c r="A866" t="s">
         <v>267</v>
       </c>
@@ -13872,7 +13906,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="867" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:8" ns3:dyDescent="0.2">
       <c r="A867" t="s">
         <v>269</v>
       </c>
@@ -13896,8 +13930,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O867" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O867" ns2:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" ns4:id="rId1"/>
 </worksheet>
 </file>
--- a/premise/data/additional_inventories/lci-batteries-NMC111-811-NCA-LFP.xlsx
+++ b/premise/data/additional_inventories/lci-batteries-NMC111-811-NCA-LFP.xlsx
@@ -13638,6 +13638,11 @@
       <c r="H854" t="s">
         <v>6</v>
       </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="855" spans="1:8" ns3:dyDescent="0.2">
       <c r="A855" t="s">
@@ -13658,6 +13663,11 @@
       <c r="G855" t="s">
         <v>136</v>
       </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>APPROVED SBR PROCESS-WATER VOLUME REFERENCE, issue102, 2026-10-18. Crenna2021 DOI10.1016/j.resconrec.2021.105619 documentsSBRasbatterybinder;recoveredSI doesnotverifythemanufacturing-waterrecipe. TheexistingpremiseSBRprovidercontains1.8kgdeionizedprocesswater/kgdrySBRand0.25m3coolingwaterresource;threecopieshave1.8m3unpollutedWWT. Sourcewater-to-wastewatertreatmentbasiswasnotindependentlyrecovered;thisisexplicitphysicalreferencecorrection,notclaimedverifiedsourceerratum. Existing1.8m3processWWTis1800kgliquidandcannotfollowfrom1.8kgprocesswater plus250kgcoolingwaterwithoutunreported&gt;1548kgwaterfeed. Modelall1.8kgdeionizedprocesswaterassenttoprocessWWT:1.8/1000=0.0018m3at1000kg/m3. Thisassignmentisexplicitengineeringwaterfate;sourceoriginalWWTunitnotverified,notclaimthatallindustrialsewerisexactly1.8L. Keep0.25m3coolingwithdrawal,separatefromprocesswater;coolingreturncompartment/temperatureandconsumptivefractionremainunresolvedandarenotinvented.0-100%coolingreturn sensitivityrequired;noextra0.25m3WWTassumed. Existingheat/emissionquantitiesretained,notinventfullthermalbalance. Polymermonomers,output1kgdrySBR,energyandallmetalcoefficients unchanged. Samecorrectioninall3copiespreventsdefaultversion/importorderfromrestoringwrongvolume. DoesnotvalidateSBRwastewaterpollutantloadorwholeindustrialwaterbalance.</t>
+        </is>
+      </c>
     </row>
     <row r="856" spans="1:8" ns3:dyDescent="0.2">
       <c r="A856" t="s">
@@ -13911,7 +13921,7 @@
         <v>269</v>
       </c>
       <c r="B867">
-        <v>-1.8</v>
+        <v>-0.0018</v>
       </c>
       <c r="C867" t="s">
         <v>222</v>
@@ -13927,6 +13937,11 @@
       </c>
       <c r="H867" t="s">
         <v>270</v>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>APPROVED SBR PROCESS-WATER VOLUME REFERENCE, issue102, 2026-10-18. Crenna2021 DOI10.1016/j.resconrec.2021.105619 documentsSBRasbatterybinder;recoveredSI doesnotverifythemanufacturing-waterrecipe. TheexistingpremiseSBRprovidercontains1.8kgdeionizedprocesswater/kgdrySBRand0.25m3coolingwaterresource;threecopieshave1.8m3unpollutedWWT. Sourcewater-to-wastewatertreatmentbasiswasnotindependentlyrecovered;thisisexplicitphysicalreferencecorrection,notclaimedverifiedsourceerratum. Existing1.8m3processWWTis1800kgliquidandcannotfollowfrom1.8kgprocesswater plus250kgcoolingwaterwithoutunreported&gt;1548kgwaterfeed. Modelall1.8kgdeionizedprocesswaterassenttoprocessWWT:1.8/1000=0.0018m3at1000kg/m3. Thisassignmentisexplicitengineeringwaterfate;sourceoriginalWWTunitnotverified,notclaimthatallindustrialsewerisexactly1.8L. Keep0.25m3coolingwithdrawal,separatefromprocesswater;coolingreturncompartment/temperatureandconsumptivefractionremainunresolvedandarenotinvented.0-100%coolingreturn sensitivityrequired;noextra0.25m3WWTassumed. Existingheat/emissionquantitiesretained,notinventfullthermalbalance. Polymermonomers,output1kgdrySBR,energyandallmetalcoefficients unchanged. Samecorrectioninall3copiespreventsdefaultversion/importorderfromrestoringwrongvolume. DoesnotvalidateSBRwastewaterpollutantloadorwholeindustrialwaterbalance.</t>
+        </is>
       </c>
     </row>
   </sheetData>
